--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_9.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_9.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.02883607968025934</v>
+        <v>0.02415778769974686</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008458258475039731</v>
+        <v>0.008452235047349248</v>
       </c>
       <c r="C2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>38650649</v>
+        <v>4150804</v>
       </c>
       <c r="L2" t="n">
-        <v>20268768</v>
+        <v>1753527</v>
       </c>
       <c r="M2" t="n">
-        <v>4708767</v>
+        <v>345305</v>
       </c>
       <c r="N2" t="n">
-        <v>195298</v>
+        <v>8837</v>
       </c>
       <c r="O2" t="n">
-        <v>2856216</v>
+        <v>205371</v>
       </c>
       <c r="P2" t="n">
-        <v>1113264</v>
+        <v>68710</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999743700027466</v>
+        <v>0.9999318718910217</v>
       </c>
       <c r="R2" t="n">
-        <v>0.832058310508728</v>
+        <v>0.7428401112556458</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6922691464424133</v>
+        <v>0.5782650709152222</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6143547892570496</v>
+        <v>0.4612763226032257</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2412504106760025</v>
+        <v>0.06590939313173294</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6681650876998901</v>
+        <v>0.5009525418281555</v>
       </c>
       <c r="W2" t="n">
-        <v>0.778370201587677</v>
+        <v>0.6643461585044861</v>
       </c>
       <c r="X2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,469 +742,469 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>56666493</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>43037872</v>
+        <v>4763805</v>
       </c>
       <c r="AG2" t="n">
-        <v>26773490</v>
+        <v>3006353</v>
       </c>
       <c r="AH2" t="n">
-        <v>7206453</v>
+        <v>805109</v>
       </c>
       <c r="AI2" t="n">
-        <v>530962</v>
+        <v>59219</v>
       </c>
       <c r="AJ2" t="n">
-        <v>4135986</v>
+        <v>460827</v>
       </c>
       <c r="AK2" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559941291809082</v>
+        <v>0.9549221992492676</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116339683532715</v>
+        <v>0.912146270275116</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8583457469940186</v>
+        <v>0.8583800792694092</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.661908745765686</v>
+        <v>0.6608968377113342</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020386338233948</v>
+        <v>0.9020029902458191</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314467906951904</v>
+        <v>0.9314685463905334</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.007470890377778792</v>
+        <v>0.006125972134522664</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002028316989047001</v>
+        <v>0.002026323576521127</v>
       </c>
       <c r="C3" t="n">
-        <v>1060</v>
+        <v>354</v>
       </c>
       <c r="D3" t="n">
-        <v>38650649</v>
+        <v>4150804</v>
       </c>
       <c r="E3" t="n">
-        <v>6078814</v>
+        <v>788268</v>
       </c>
       <c r="F3" t="n">
-        <v>185073</v>
+        <v>31151</v>
       </c>
       <c r="G3" t="n">
-        <v>16826</v>
+        <v>2859</v>
       </c>
       <c r="H3" t="n">
-        <v>12467</v>
+        <v>2072</v>
       </c>
       <c r="I3" t="n">
-        <v>740</v>
+        <v>147</v>
       </c>
       <c r="J3" t="n">
-        <v>89909654</v>
+        <v>10016192</v>
       </c>
       <c r="K3" t="n">
-        <v>93830768</v>
+        <v>9917000</v>
       </c>
       <c r="L3" t="n">
-        <v>108139445</v>
+        <v>11744410</v>
       </c>
       <c r="M3" t="n">
-        <v>135216353</v>
+        <v>14986440</v>
       </c>
       <c r="N3" t="n">
-        <v>145160406</v>
+        <v>16114662</v>
       </c>
       <c r="O3" t="n">
-        <v>140571023</v>
+        <v>15613629</v>
       </c>
       <c r="P3" t="n">
-        <v>144519806</v>
+        <v>16101199</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8599423170089722</v>
+        <v>0.8342226147651672</v>
       </c>
       <c r="S3" t="n">
-        <v>0.688753604888916</v>
+        <v>0.5303554534912109</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5602046251296997</v>
+        <v>0.3673930466175079</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2432201504707336</v>
+        <v>0.09852057695388794</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6225301027297974</v>
+        <v>0.4016007781028748</v>
       </c>
       <c r="W3" t="n">
-        <v>0.639509916305542</v>
+        <v>0.3547494411468506</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>43037872</v>
+        <v>4763805</v>
       </c>
       <c r="Z3" t="n">
-        <v>1770047</v>
+        <v>196543</v>
       </c>
       <c r="AA3" t="n">
-        <v>76085</v>
+        <v>8427</v>
       </c>
       <c r="AB3" t="n">
-        <v>61120</v>
+        <v>6839</v>
       </c>
       <c r="AC3" t="n">
-        <v>235</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>270</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>89911107</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>99650873</v>
+        <v>11129066</v>
       </c>
       <c r="AG3" t="n">
-        <v>114554222</v>
+        <v>12733718</v>
       </c>
       <c r="AH3" t="n">
-        <v>136982866</v>
+        <v>15256890</v>
       </c>
       <c r="AI3" t="n">
-        <v>145503426</v>
+        <v>16209518</v>
       </c>
       <c r="AJ3" t="n">
-        <v>141540355</v>
+        <v>15768153</v>
       </c>
       <c r="AK3" t="n">
-        <v>144717483</v>
+        <v>16122647</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575541019439697</v>
+        <v>0.95742267370224</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097907543182373</v>
+        <v>0.9092735648155212</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8573557138442993</v>
+        <v>0.8566092252731323</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6612492799758911</v>
+        <v>0.6602116227149963</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014639258384705</v>
+        <v>0.9011421799659729</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312204718589783</v>
+        <v>0.931006908416748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0666158335771036</v>
+        <v>0.05776734946928563</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0319910069736064</v>
+        <v>0.03197108341586186</v>
       </c>
       <c r="C4" t="n">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="D4" t="n">
-        <v>7238480</v>
+        <v>1311550</v>
       </c>
       <c r="E4" t="n">
-        <v>20268768</v>
+        <v>1753527</v>
       </c>
       <c r="F4" t="n">
-        <v>1628469</v>
+        <v>191702</v>
       </c>
       <c r="G4" t="n">
-        <v>90853</v>
+        <v>18434</v>
       </c>
       <c r="H4" t="n">
-        <v>183178</v>
+        <v>28187</v>
       </c>
       <c r="I4" t="n">
-        <v>18334</v>
+        <v>2876</v>
       </c>
       <c r="J4" t="n">
-        <v>1453</v>
+        <v>430</v>
       </c>
       <c r="K4" t="n">
-        <v>7801203</v>
+        <v>1436945</v>
       </c>
       <c r="L4" t="n">
-        <v>9009971</v>
+        <v>1278866</v>
       </c>
       <c r="M4" t="n">
-        <v>2955806</v>
+        <v>403281</v>
       </c>
       <c r="N4" t="n">
-        <v>614226</v>
+        <v>125241</v>
       </c>
       <c r="O4" t="n">
-        <v>1418500</v>
+        <v>204590</v>
       </c>
       <c r="P4" t="n">
-        <v>316986</v>
+        <v>34715</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999871850013733</v>
+        <v>0.9999659657478333</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8457705974578857</v>
+        <v>0.7858837842941284</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6905069351196289</v>
+        <v>0.5532750487327576</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5860314965248108</v>
+        <v>0.409016489982605</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2422312796115875</v>
+        <v>0.07898112386465073</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6445408463478088</v>
+        <v>0.4458084106445312</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7021404504776001</v>
+        <v>0.4625207185745239</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1850168</v>
+        <v>210159</v>
       </c>
       <c r="Z4" t="n">
-        <v>26773490</v>
+        <v>3006353</v>
       </c>
       <c r="AA4" t="n">
-        <v>744102</v>
+        <v>83023</v>
       </c>
       <c r="AB4" t="n">
-        <v>49580</v>
+        <v>5590</v>
       </c>
       <c r="AC4" t="n">
-        <v>10232</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>612</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1981098</v>
+        <v>224879</v>
       </c>
       <c r="AG4" t="n">
-        <v>2595194</v>
+        <v>289558</v>
       </c>
       <c r="AH4" t="n">
-        <v>1189293</v>
+        <v>132831</v>
       </c>
       <c r="AI4" t="n">
-        <v>271206</v>
+        <v>30385</v>
       </c>
       <c r="AJ4" t="n">
-        <v>449168</v>
+        <v>50066</v>
       </c>
       <c r="AK4" t="n">
-        <v>119309</v>
+        <v>13267</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567735195159912</v>
+        <v>0.9561707377433777</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910711407661438</v>
+        <v>0.9107076525688171</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8578504323959351</v>
+        <v>0.8574937582015991</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6615788340568542</v>
+        <v>0.660554051399231</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017512202262878</v>
+        <v>0.9015724062919617</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.931333601474762</v>
+        <v>0.9312376976013184</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>398715</v>
+        <v>93402</v>
       </c>
       <c r="E5" t="n">
-        <v>2389151</v>
+        <v>382822</v>
       </c>
       <c r="F5" t="n">
-        <v>4708767</v>
+        <v>345305</v>
       </c>
       <c r="G5" t="n">
-        <v>206265</v>
+        <v>34817</v>
       </c>
       <c r="H5" t="n">
-        <v>636034</v>
+        <v>74167</v>
       </c>
       <c r="I5" t="n">
-        <v>66441</v>
+        <v>9352</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>6294980</v>
+        <v>824851</v>
       </c>
       <c r="L5" t="n">
-        <v>9159416</v>
+        <v>1552797</v>
       </c>
       <c r="M5" t="n">
-        <v>3696674</v>
+        <v>594574</v>
       </c>
       <c r="N5" t="n">
-        <v>607670</v>
+        <v>80860</v>
       </c>
       <c r="O5" t="n">
-        <v>1731861</v>
+        <v>306010</v>
       </c>
       <c r="P5" t="n">
-        <v>627544</v>
+        <v>124976</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999901056289673</v>
+        <v>0.9999736547470093</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9038312435150146</v>
+        <v>0.8614910244941711</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8760425448417664</v>
+        <v>0.8265932202339172</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9546146392822266</v>
+        <v>0.9388928413391113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9916638135910034</v>
+        <v>0.9873786568641663</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9785072207450867</v>
+        <v>0.9687316417694092</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9935560822486877</v>
+        <v>0.9902207851409912</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>72118</v>
+        <v>8098</v>
       </c>
       <c r="Z5" t="n">
-        <v>769074</v>
+        <v>86770</v>
       </c>
       <c r="AA5" t="n">
-        <v>7206453</v>
+        <v>805109</v>
       </c>
       <c r="AB5" t="n">
-        <v>89663</v>
+        <v>10018</v>
       </c>
       <c r="AC5" t="n">
-        <v>262436</v>
+        <v>29251</v>
       </c>
       <c r="AD5" t="n">
-        <v>5697</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1907757</v>
+        <v>211850</v>
       </c>
       <c r="AG5" t="n">
-        <v>2654694</v>
+        <v>299971</v>
       </c>
       <c r="AH5" t="n">
-        <v>1198988</v>
+        <v>134770</v>
       </c>
       <c r="AI5" t="n">
-        <v>272006</v>
+        <v>30478</v>
       </c>
       <c r="AJ5" t="n">
-        <v>452091</v>
+        <v>50554</v>
       </c>
       <c r="AK5" t="n">
-        <v>119732</v>
+        <v>13363</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734689593315125</v>
+        <v>0.9732553958892822</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641835689544678</v>
+        <v>0.9638981223106384</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837063550949097</v>
+        <v>0.9836125373840332</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962940216064453</v>
+        <v>0.99627286195755</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938513040542603</v>
+        <v>0.9938381910324097</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983691573143005</v>
+        <v>0.9983692169189453</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>129419</v>
+        <v>21240</v>
       </c>
       <c r="E6" t="n">
-        <v>177768</v>
+        <v>24312</v>
       </c>
       <c r="F6" t="n">
-        <v>198668</v>
+        <v>25671</v>
       </c>
       <c r="G6" t="n">
-        <v>195298</v>
+        <v>8837</v>
       </c>
       <c r="H6" t="n">
-        <v>91840</v>
+        <v>8613</v>
       </c>
       <c r="I6" t="n">
-        <v>9903</v>
+        <v>1014</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>58389</v>
+        <v>6586</v>
       </c>
       <c r="Z6" t="n">
-        <v>48057</v>
+        <v>5354</v>
       </c>
       <c r="AA6" t="n">
-        <v>98343</v>
+        <v>11038</v>
       </c>
       <c r="AB6" t="n">
-        <v>530962</v>
+        <v>59219</v>
       </c>
       <c r="AC6" t="n">
-        <v>62888</v>
+        <v>7019</v>
       </c>
       <c r="AD6" t="n">
-        <v>4329</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>33079</v>
+        <v>10334</v>
       </c>
       <c r="E7" t="n">
-        <v>333892</v>
+        <v>75593</v>
       </c>
       <c r="F7" t="n">
-        <v>875238</v>
+        <v>139446</v>
       </c>
       <c r="G7" t="n">
-        <v>268021</v>
+        <v>59311</v>
       </c>
       <c r="H7" t="n">
-        <v>2856216</v>
+        <v>205371</v>
       </c>
       <c r="I7" t="n">
-        <v>221568</v>
+        <v>21326</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>171</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>7287</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>267782</v>
+        <v>30010</v>
       </c>
       <c r="AB7" t="n">
-        <v>68450</v>
+        <v>7671</v>
       </c>
       <c r="AC7" t="n">
-        <v>4135986</v>
+        <v>460827</v>
       </c>
       <c r="AD7" t="n">
-        <v>108401</v>
+        <v>12055</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>1510</v>
+        <v>419</v>
       </c>
       <c r="E8" t="n">
-        <v>30346</v>
+        <v>7871</v>
       </c>
       <c r="F8" t="n">
-        <v>68358</v>
+        <v>15311</v>
       </c>
       <c r="G8" t="n">
-        <v>32261</v>
+        <v>9820</v>
       </c>
       <c r="H8" t="n">
-        <v>494981</v>
+        <v>91551</v>
       </c>
       <c r="I8" t="n">
-        <v>1113264</v>
+        <v>68710</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>252</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>729</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2981</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2393</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>113377</v>
+        <v>12654</v>
       </c>
       <c r="AD8" t="n">
-        <v>1621076</v>
+        <v>180323</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
